--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-drugs.xlsx
+++ b/dev/CodeSystem-drugs.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
